--- a/week-01/Ex4A_GTrends.xlsx
+++ b/week-01/Ex4A_GTrends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dahliasanchez\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAED2E43-DD9B-4CAE-84BF-CA8EC1174931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FDAD4F0-0173-4211-AEBD-E378E38C44BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D3B15F1C-A032-44A9-814F-B3EAEA8FB868}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{145BFC04-B76D-437D-95AD-B9755A137C50}"/>
   </bookViews>
   <sheets>
     <sheet name="GTrends_milkshake_hamburger_202" sheetId="1" r:id="rId1"/>
@@ -20,21 +20,174 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Category: All categories</t>
   </si>
   <si>
-    <t>Week</t>
-  </si>
-  <si>
-    <t>Milkshake: (United States)</t>
-  </si>
-  <si>
-    <t>Hamburger: (United States)</t>
-  </si>
-  <si>
-    <t>Breakup: (United States)</t>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Milkshake: (2/1/24 - 2/28/25)</t>
+  </si>
+  <si>
+    <t>Hamburger: (2/1/24 - 2/28/25)</t>
+  </si>
+  <si>
+    <t>Breakup: (2/1/24 - 2/28/25)</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>Wyoming</t>
+  </si>
+  <si>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Hawaii</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>District of Columbia</t>
   </si>
 </sst>
 </file>
@@ -520,7 +673,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -895,8 +1048,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C43FDED8-3A51-42D9-A6B4-6CE0D7D39F4A}">
-  <dimension ref="A1:D60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04756468-C8F3-4DB6-9613-07BF1EE00970}">
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -919,801 +1072,717 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>45319</v>
-      </c>
-      <c r="B4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="C4">
-        <v>66</v>
-      </c>
-      <c r="D4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>45326</v>
-      </c>
-      <c r="B5">
+      <c r="B22" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>26</v>
       </c>
-      <c r="C5">
-        <v>70</v>
-      </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>45333</v>
-      </c>
-      <c r="B6">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>64</v>
-      </c>
-      <c r="D6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>45340</v>
-      </c>
-      <c r="B7">
-        <v>25</v>
-      </c>
-      <c r="C7">
-        <v>70</v>
-      </c>
-      <c r="D7">
+      <c r="B25" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>45347</v>
-      </c>
-      <c r="B8">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>68</v>
-      </c>
-      <c r="D8">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>45354</v>
-      </c>
-      <c r="B9">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>67</v>
-      </c>
-      <c r="D9">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>45361</v>
-      </c>
-      <c r="B10">
-        <v>26</v>
-      </c>
-      <c r="C10">
-        <v>72</v>
-      </c>
-      <c r="D10">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>45368</v>
-      </c>
-      <c r="B11">
-        <v>27</v>
-      </c>
-      <c r="C11">
-        <v>66</v>
-      </c>
-      <c r="D11">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>45375</v>
-      </c>
-      <c r="B12">
-        <v>23</v>
-      </c>
-      <c r="C12">
-        <v>64</v>
-      </c>
-      <c r="D12">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>45382</v>
-      </c>
-      <c r="B13">
-        <v>21</v>
-      </c>
-      <c r="C13">
-        <v>63</v>
-      </c>
-      <c r="D13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>45389</v>
-      </c>
-      <c r="B14">
-        <v>21</v>
-      </c>
-      <c r="C14">
-        <v>66</v>
-      </c>
-      <c r="D14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
-        <v>45396</v>
-      </c>
-      <c r="B15">
-        <v>23</v>
-      </c>
-      <c r="C15">
-        <v>71</v>
-      </c>
-      <c r="D15">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
-        <v>45403</v>
-      </c>
-      <c r="B16">
-        <v>22</v>
-      </c>
-      <c r="C16">
-        <v>69</v>
-      </c>
-      <c r="D16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
-        <v>45410</v>
-      </c>
-      <c r="B17">
-        <v>23</v>
-      </c>
-      <c r="C17">
-        <v>77</v>
-      </c>
-      <c r="D17">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
-        <v>45417</v>
-      </c>
-      <c r="B18">
-        <v>22</v>
-      </c>
-      <c r="C18">
-        <v>67</v>
-      </c>
-      <c r="D18">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
-        <v>45424</v>
-      </c>
-      <c r="B19">
-        <v>21</v>
-      </c>
-      <c r="C19">
-        <v>67</v>
-      </c>
-      <c r="D19">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
-        <v>45431</v>
-      </c>
-      <c r="B20">
-        <v>21</v>
-      </c>
-      <c r="C20">
-        <v>76</v>
-      </c>
-      <c r="D20">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
-        <v>45438</v>
-      </c>
-      <c r="B21">
-        <v>22</v>
-      </c>
-      <c r="C21">
-        <v>100</v>
-      </c>
-      <c r="D21">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
-        <v>45445</v>
-      </c>
-      <c r="B22">
-        <v>23</v>
-      </c>
-      <c r="C22">
-        <v>73</v>
-      </c>
-      <c r="D22">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
-        <v>45452</v>
-      </c>
-      <c r="B23">
-        <v>22</v>
-      </c>
-      <c r="C23">
-        <v>72</v>
-      </c>
-      <c r="D23">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
-        <v>45459</v>
-      </c>
-      <c r="B24">
-        <v>22</v>
-      </c>
-      <c r="C24">
-        <v>73</v>
-      </c>
-      <c r="D24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
-        <v>45466</v>
-      </c>
-      <c r="B25">
-        <v>23</v>
-      </c>
-      <c r="C25">
-        <v>73</v>
-      </c>
-      <c r="D25">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
-        <v>45473</v>
-      </c>
-      <c r="B26">
-        <v>23</v>
-      </c>
-      <c r="C26">
-        <v>96</v>
-      </c>
-      <c r="D26">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
-        <v>45480</v>
-      </c>
-      <c r="B27">
-        <v>24</v>
-      </c>
-      <c r="C27">
-        <v>71</v>
-      </c>
-      <c r="D27">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
-        <v>45487</v>
-      </c>
-      <c r="B28">
-        <v>23</v>
-      </c>
-      <c r="C28">
-        <v>71</v>
-      </c>
-      <c r="D28">
-        <v>13</v>
+      <c r="B28" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
-        <v>45494</v>
-      </c>
-      <c r="B29">
-        <v>22</v>
-      </c>
-      <c r="C29">
-        <v>69</v>
-      </c>
-      <c r="D29">
-        <v>14</v>
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.16</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
-        <v>45501</v>
-      </c>
-      <c r="B30">
-        <v>21</v>
-      </c>
-      <c r="C30">
-        <v>68</v>
-      </c>
-      <c r="D30">
-        <v>12</v>
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
-        <v>45508</v>
-      </c>
-      <c r="B31">
-        <v>23</v>
-      </c>
-      <c r="C31">
-        <v>67</v>
-      </c>
-      <c r="D31">
-        <v>10</v>
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.11</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
-        <v>45515</v>
-      </c>
-      <c r="B32">
-        <v>24</v>
-      </c>
-      <c r="C32">
-        <v>67</v>
-      </c>
-      <c r="D32">
-        <v>10</v>
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
-        <v>45522</v>
-      </c>
-      <c r="B33">
-        <v>22</v>
-      </c>
-      <c r="C33">
-        <v>69</v>
-      </c>
-      <c r="D33">
-        <v>11</v>
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.13</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
-        <v>45529</v>
-      </c>
-      <c r="B34">
-        <v>23</v>
-      </c>
-      <c r="C34">
-        <v>69</v>
-      </c>
-      <c r="D34">
-        <v>11</v>
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.13</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
-        <v>45536</v>
-      </c>
-      <c r="B35">
-        <v>21</v>
-      </c>
-      <c r="C35">
-        <v>68</v>
-      </c>
-      <c r="D35">
-        <v>17</v>
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
-        <v>45543</v>
-      </c>
-      <c r="B36">
-        <v>19</v>
-      </c>
-      <c r="C36">
-        <v>64</v>
-      </c>
-      <c r="D36">
-        <v>12</v>
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.13</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
-        <v>45550</v>
-      </c>
-      <c r="B37">
-        <v>19</v>
-      </c>
-      <c r="C37">
-        <v>72</v>
-      </c>
-      <c r="D37">
-        <v>12</v>
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.16</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="1">
-        <v>45557</v>
-      </c>
-      <c r="B38">
-        <v>20</v>
-      </c>
-      <c r="C38">
-        <v>59</v>
-      </c>
-      <c r="D38">
-        <v>12</v>
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.12</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
-        <v>45564</v>
-      </c>
-      <c r="B39">
-        <v>19</v>
-      </c>
-      <c r="C39">
-        <v>61</v>
-      </c>
-      <c r="D39">
-        <v>14</v>
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.16</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="1">
-        <v>45571</v>
-      </c>
-      <c r="B40">
-        <v>20</v>
-      </c>
-      <c r="C40">
-        <v>62</v>
-      </c>
-      <c r="D40">
-        <v>12</v>
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0.12</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
-        <v>45578</v>
-      </c>
-      <c r="B41">
-        <v>19</v>
-      </c>
-      <c r="C41">
-        <v>60</v>
-      </c>
-      <c r="D41">
-        <v>14</v>
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
-        <v>45585</v>
-      </c>
-      <c r="B42">
-        <v>19</v>
-      </c>
-      <c r="C42">
-        <v>62</v>
-      </c>
-      <c r="D42">
-        <v>14</v>
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.13</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="1">
-        <v>45592</v>
-      </c>
-      <c r="B43">
-        <v>18</v>
-      </c>
-      <c r="C43">
-        <v>61</v>
-      </c>
-      <c r="D43">
-        <v>13</v>
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0.17</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="1">
-        <v>45599</v>
-      </c>
-      <c r="B44">
-        <v>18</v>
-      </c>
-      <c r="C44">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>55</v>
       </c>
-      <c r="D44">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
-        <v>45606</v>
-      </c>
-      <c r="B45">
-        <v>21</v>
-      </c>
-      <c r="C45">
-        <v>58</v>
-      </c>
-      <c r="D45">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
-        <v>45613</v>
-      </c>
-      <c r="B46">
-        <v>20</v>
-      </c>
-      <c r="C46">
-        <v>57</v>
-      </c>
-      <c r="D46">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
-        <v>45620</v>
-      </c>
-      <c r="B47">
-        <v>17</v>
-      </c>
-      <c r="C47">
-        <v>50</v>
-      </c>
-      <c r="D47">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
-        <v>45627</v>
-      </c>
-      <c r="B48">
-        <v>18</v>
-      </c>
-      <c r="C48">
-        <v>53</v>
-      </c>
-      <c r="D48">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
-        <v>45634</v>
-      </c>
-      <c r="B49">
-        <v>18</v>
-      </c>
-      <c r="C49">
-        <v>56</v>
-      </c>
-      <c r="D49">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
-        <v>45641</v>
-      </c>
-      <c r="B50">
-        <v>18</v>
-      </c>
-      <c r="C50">
-        <v>56</v>
-      </c>
-      <c r="D50">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
-        <v>45648</v>
-      </c>
-      <c r="B51">
-        <v>17</v>
-      </c>
-      <c r="C51">
-        <v>56</v>
-      </c>
-      <c r="D51">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
-        <v>45655</v>
-      </c>
-      <c r="B52">
-        <v>23</v>
-      </c>
-      <c r="C52">
-        <v>65</v>
-      </c>
-      <c r="D52">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
-        <v>45662</v>
-      </c>
-      <c r="B53">
-        <v>24</v>
-      </c>
-      <c r="C53">
-        <v>65</v>
-      </c>
-      <c r="D53">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
-        <v>45669</v>
-      </c>
-      <c r="B54">
-        <v>25</v>
-      </c>
-      <c r="C54">
-        <v>64</v>
-      </c>
-      <c r="D54">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
-        <v>45676</v>
-      </c>
-      <c r="B55">
-        <v>23</v>
-      </c>
-      <c r="C55">
-        <v>62</v>
-      </c>
-      <c r="D55">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
-        <v>45683</v>
-      </c>
-      <c r="B56">
-        <v>24</v>
-      </c>
-      <c r="C56">
-        <v>64</v>
-      </c>
-      <c r="D56">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
-        <v>45690</v>
-      </c>
-      <c r="B57">
-        <v>28</v>
-      </c>
-      <c r="C57">
-        <v>65</v>
-      </c>
-      <c r="D57">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
-        <v>45697</v>
-      </c>
-      <c r="B58">
-        <v>24</v>
-      </c>
-      <c r="C58">
-        <v>63</v>
-      </c>
-      <c r="D58">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="1">
-        <v>45704</v>
-      </c>
-      <c r="B59">
-        <v>26</v>
-      </c>
-      <c r="C59">
-        <v>68</v>
-      </c>
-      <c r="D59">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
-        <v>45711</v>
-      </c>
-      <c r="B60">
-        <v>28</v>
-      </c>
-      <c r="C60">
-        <v>68</v>
-      </c>
-      <c r="D60">
-        <v>14</v>
+      <c r="B54" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>

--- a/week-01/Ex4A_GTrends.xlsx
+++ b/week-01/Ex4A_GTrends.xlsx
@@ -1,200 +1,222 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dahliasanchez\Documents\DataAnalytics\week-01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/dsanchez1_my_yearupunited_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FDAD4F0-0173-4211-AEBD-E378E38C44BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{605DE4E4-78FA-45B0-B96E-3C6A167EF537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{145BFC04-B76D-437D-95AD-B9755A137C50}"/>
   </bookViews>
   <sheets>
     <sheet name="GTrends_milkshake_hamburger_202" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GTrends_milkshake_hamburger_202!$A$1:$E$52</definedName>
+  </definedNames>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
-  <si>
-    <t>Category: All categories</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+  <si>
+    <t>RegionID</t>
   </si>
   <si>
     <t>Region</t>
   </si>
   <si>
+    <t>Hamburger: (2/1/24 - 2/28/25)</t>
+  </si>
+  <si>
     <t>Milkshake: (2/1/24 - 2/28/25)</t>
   </si>
   <si>
-    <t>Hamburger: (2/1/24 - 2/28/25)</t>
-  </si>
-  <si>
     <t>Breakup: (2/1/24 - 2/28/25)</t>
   </si>
   <si>
+    <t># of Region</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>District of Columbia</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Hawaii</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
     <t>South Carolina</t>
   </si>
   <si>
-    <t>Alabama</t>
-  </si>
-  <si>
-    <t>Kentucky</t>
+    <t>South Dakota</t>
   </si>
   <si>
     <t>Tennessee</t>
   </si>
   <si>
-    <t>Indiana</t>
+    <t>Texas</t>
   </si>
   <si>
     <t>Utah</t>
   </si>
   <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>Maryland</t>
-  </si>
-  <si>
-    <t>Illinois</t>
-  </si>
-  <si>
-    <t>North Carolina</t>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>Washington</t>
   </si>
   <si>
     <t>West Virginia</t>
   </si>
   <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Pennsylvania</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
-    <t>Nevada</t>
-  </si>
-  <si>
-    <t>Idaho</t>
-  </si>
-  <si>
-    <t>Virginia</t>
-  </si>
-  <si>
-    <t>Connecticut</t>
-  </si>
-  <si>
-    <t>Delaware</t>
-  </si>
-  <si>
-    <t>Mississippi</t>
-  </si>
-  <si>
-    <t>Michigan</t>
-  </si>
-  <si>
-    <t>Missouri</t>
-  </si>
-  <si>
-    <t>Florida</t>
-  </si>
-  <si>
-    <t>Kansas</t>
-  </si>
-  <si>
-    <t>New Jersey</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Oklahoma</t>
-  </si>
-  <si>
     <t>Wisconsin</t>
   </si>
   <si>
-    <t>Minnesota</t>
-  </si>
-  <si>
-    <t>Louisiana</t>
-  </si>
-  <si>
-    <t>Arizona</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>North Dakota</t>
-  </si>
-  <si>
-    <t>New York</t>
-  </si>
-  <si>
-    <t>Nebraska</t>
-  </si>
-  <si>
-    <t>New Mexico</t>
-  </si>
-  <si>
-    <t>Oregon</t>
-  </si>
-  <si>
-    <t>Massachusetts</t>
-  </si>
-  <si>
-    <t>Washington</t>
-  </si>
-  <si>
-    <t>New Hampshire</t>
-  </si>
-  <si>
-    <t>Colorado</t>
-  </si>
-  <si>
-    <t>South Dakota</t>
-  </si>
-  <si>
-    <t>Maine</t>
-  </si>
-  <si>
     <t>Wyoming</t>
-  </si>
-  <si>
-    <t>Vermont</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Hawaii</t>
-  </si>
-  <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>District of Columbia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,7 +352,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -508,6 +530,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -671,9 +699,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1049,743 +1078,1092 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04756468-C8F3-4DB6-9613-07BF1EE00970}">
-  <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2">
+        <f>COUNTA(B2:B52)</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>2</v>
+      </c>
       <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B4" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.24</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.23</v>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>0.63</v>
       </c>
       <c r="D6" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E8" s="1">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="9" spans="1:8">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E9" s="1">
         <v>0.13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="10" spans="1:8">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D12" s="1">
         <v>0.24</v>
       </c>
-      <c r="C8" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="E12" s="1">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="D9" s="1">
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E13" s="1">
         <v>0.13</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.24</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="D10" s="1">
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E15" s="1">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="16" spans="1:8">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B14" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="1">
-        <v>0.23</v>
+      <c r="B16" t="s">
+        <v>20</v>
       </c>
       <c r="C16" s="1">
         <v>0.62</v>
       </c>
       <c r="D16" s="1">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0.2</v>
+        <v>0.24</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
       </c>
       <c r="C17" s="1">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="D17" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E17" s="1">
         <v>0.13</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.21</v>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
       </c>
       <c r="C18" s="1">
         <v>0.66</v>
       </c>
       <c r="D18" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E20" s="1">
         <v>0.13</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="21" spans="1:5">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B19" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="D19" s="1">
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E21" s="1">
         <v>0.13</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B20" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B21" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B22" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0.21</v>
+      <c r="B24" t="s">
+        <v>28</v>
       </c>
       <c r="C24" s="1">
         <v>0.67</v>
       </c>
       <c r="D24" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E24" s="1">
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D32" s="1">
         <v>0.21</v>
       </c>
-      <c r="C25" s="1">
+      <c r="E32" s="1">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="1">
         <v>0.67</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D33" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E35" s="1">
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="1">
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D36" s="1">
         <v>0.19</v>
       </c>
-      <c r="C26" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="D26" s="1">
+      <c r="E36" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E37" s="1">
         <v>0.13</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="1">
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="D40" s="1">
         <v>0.23</v>
       </c>
-      <c r="C27" s="1">
+      <c r="E40" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="1">
         <v>0.63</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D41" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E41" s="1">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="C28" s="1">
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="1">
         <v>0.66</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D42" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D43" s="1">
         <v>0.14000000000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="D31" s="1">
+      <c r="E43" s="1">
         <v>0.11</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="D33" s="1">
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="E44" s="1">
         <v>0.13</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="C34" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="D36" s="1">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="C37" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C38" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="C39" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="D40" s="1">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C41" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="D41" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="C42" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="D42" s="1">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+    <row r="45" spans="1:5">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B43" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="C43" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="D43" s="1">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="C44" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="D44" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45" s="1">
-        <v>0.2</v>
+      <c r="B45" t="s">
+        <v>49</v>
       </c>
       <c r="C45" s="1">
         <v>0.67</v>
       </c>
       <c r="D45" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E45" s="1">
         <v>0.13</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D52" s="1">
         <v>0.17</v>
       </c>
-      <c r="C46" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="D46" s="1">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47" s="1">
+      <c r="E52" s="1">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C47" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="D47" s="1">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="C48" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="D48" s="1">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="C49" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="D49" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="1">
-        <v>0.16</v>
-      </c>
-      <c r="C50" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="D50" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="D51" s="1">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="D52" s="1">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="C53" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="D53" s="1">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="C54" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="D54" s="1">
-        <v>0.17</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E52" xr:uid="{04756468-C8F3-4DB6-9613-07BF1EE00970}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E52">
+      <sortCondition ref="B1:B52"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b275f972-a0ec-44ed-acfc-93b347ca42d1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006BAB7F1D75092C43A80735B994755528" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44a867c53620602b95c719ed84922ec5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b275f972-a0ec-44ed-acfc-93b347ca42d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6e19629f965acf6c6a9affc8035138fe" ns3:_="">
+    <xsd:import namespace="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b275f972-a0ec-44ed-acfc-93b347ca42d1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="12" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6CCD296-6D00-4581-8331-4E0324AFB23D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD991CEA-FDA1-40BD-9333-EB5B33534D5D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{344B5E17-8697-4A03-8209-B01BE8F38B31}"/>
 </file>
--- a/week-01/Ex4A_GTrends.xlsx
+++ b/week-01/Ex4A_GTrends.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/dsanchez1_my_yearupunited_org/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dahliasanchez\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{605DE4E4-78FA-45B0-B96E-3C6A167EF537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -216,7 +216,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1079,16 +1079,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04756468-C8F3-4DB6-9613-07BF1EE00970}">
   <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1990,20 +1990,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="b275f972-a0ec-44ed-acfc-93b347ca42d1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b275f972-a0ec-44ed-acfc-93b347ca42d1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2157,13 +2157,37 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6CCD296-6D00-4581-8331-4E0324AFB23D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD991CEA-FDA1-40BD-9333-EB5B33534D5D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD991CEA-FDA1-40BD-9333-EB5B33534D5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6CCD296-6D00-4581-8331-4E0324AFB23D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{344B5E17-8697-4A03-8209-B01BE8F38B31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{344B5E17-8697-4A03-8209-B01BE8F38B31}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>